--- a/data/Quality control/ghg_comparison__.xlsx
+++ b/data/Quality control/ghg_comparison__.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/Quality control/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_23F921ED55A38BD86D7F8C426FB6CD627552AE68" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5339FEBA-3B94-4014-9A0D-04A14BA0B97D}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="11_23F921ED55A38BD86D7F8C426FB6CD627552AE68" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9126330-2142-49DC-B226-3444CCC9D3B2}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="new" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">new!$A$1:$G$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="48">
   <si>
     <t>tCO2eq_estimated</t>
   </si>
@@ -175,6 +176,12 @@
   </si>
   <si>
     <t>Mapping + manually collected data</t>
+  </si>
+  <si>
+    <t>Red Chris; big outliers in GHG</t>
+  </si>
+  <si>
+    <t>Brucejack; outliers for GHG doré</t>
   </si>
 </sst>
 </file>
@@ -1177,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{685CFB30-F35F-4405-9D5F-B0945D39203A}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.7265625" bestFit="1" customWidth="1"/>
@@ -1188,7 +1195,7 @@
     <col min="6" max="6" width="45.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1208,7 +1215,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1228,149 +1235,146 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>119997.1576154365</v>
-      </c>
-      <c r="C3">
-        <v>129512.8841</v>
-      </c>
-      <c r="D3">
-        <v>-9515.726484563449</v>
-      </c>
-      <c r="E3">
-        <v>0.92652679653696746</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3">
+        <v>7015.5469297352392</v>
+      </c>
+      <c r="C3" s="3">
+        <v>25315.878199999999</v>
+      </c>
+      <c r="D3" s="3">
+        <v>-18300.33127026476</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.277120425146272</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>40875.432077647783</v>
+        <v>9108.190113087674</v>
       </c>
       <c r="C4">
-        <v>27335.623950000001</v>
+        <v>26796.345969999998</v>
       </c>
       <c r="D4">
-        <v>13539.808127647781</v>
+        <v>-17688.155856912319</v>
       </c>
       <c r="E4">
-        <v>1.495317324836398</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>102581.64419203129</v>
-      </c>
-      <c r="C5">
-        <v>95697.622499999998</v>
-      </c>
-      <c r="D5">
-        <v>6884.021692031296</v>
-      </c>
-      <c r="E5">
-        <v>1.0719351381172639</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.33990418407363449</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3">
+        <v>27013.283569844811</v>
+      </c>
+      <c r="C5" s="3">
+        <v>73558.118705594999</v>
+      </c>
+      <c r="D5" s="3">
+        <v>-46544.835135750203</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.36723728182828191</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B6">
-        <v>23612.49945893959</v>
+        <v>10558.860176517979</v>
       </c>
       <c r="C6">
-        <v>15908.3</v>
+        <v>21634.757000000001</v>
       </c>
       <c r="D6">
-        <v>7704.1994589395936</v>
+        <v>-11075.89682348202</v>
       </c>
       <c r="E6">
-        <v>1.4842880420245781</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.48805078682039171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="B7">
-        <v>74891.213464487286</v>
+        <v>28000.734119851651</v>
       </c>
       <c r="C7">
-        <v>72492</v>
+        <v>45467.192990000003</v>
       </c>
       <c r="D7">
-        <v>2399.2134644872858</v>
+        <v>-17466.458870148352</v>
       </c>
       <c r="E7">
-        <v>1.0330962515103359</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.61584479442155349</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B8">
-        <v>374101.62411073368</v>
+        <v>35578.001059861519</v>
       </c>
       <c r="C8">
-        <v>253807.72769999999</v>
+        <v>56107.381999999998</v>
       </c>
       <c r="D8">
-        <v>120293.8964107338</v>
+        <v>-20529.380940138479</v>
       </c>
       <c r="E8">
-        <v>1.4739567920206149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.63410552750191629</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B9">
-        <v>63357.174757889348</v>
+        <v>9150.1771490981282</v>
       </c>
       <c r="C9">
-        <v>57797.154413883101</v>
+        <v>14214.106</v>
       </c>
       <c r="D9">
-        <v>5560.0203440062469</v>
+        <v>-5063.9288509018716</v>
       </c>
       <c r="E9">
-        <v>1.096198859621897</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="3">
-        <v>27013.283569844811</v>
-      </c>
-      <c r="C10" s="3">
-        <v>73558.118705594999</v>
-      </c>
-      <c r="D10" s="3">
-        <v>-46544.835135750203</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0.36723728182828191</v>
-      </c>
-      <c r="F10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.64373919464918361</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10">
+        <v>13637.62339983279</v>
+      </c>
+      <c r="C10">
+        <v>18188</v>
+      </c>
+      <c r="D10">
+        <v>-4550.3766001672138</v>
+      </c>
+      <c r="E10">
+        <v>0.74981435011176523</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -1389,391 +1393,400 @@
       <c r="F11" t="s">
         <v>45</v>
       </c>
-      <c r="G11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B12">
-        <v>30049.933466104401</v>
+        <v>14662.913501907869</v>
       </c>
       <c r="C12">
-        <v>23332.800200000001</v>
+        <v>16417.766</v>
       </c>
       <c r="D12">
-        <v>6717.1332661043962</v>
+        <v>-1754.85249809213</v>
       </c>
       <c r="E12">
-        <v>1.2878837177075899</v>
-      </c>
-      <c r="F12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.89311258924678727</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B13">
-        <v>146455.53884009109</v>
+        <v>30198.711343158309</v>
       </c>
       <c r="C13">
-        <v>110503.4497</v>
+        <v>33407.658000000003</v>
       </c>
       <c r="D13">
-        <v>35952.089140091062</v>
+        <v>-3208.9466568416901</v>
       </c>
       <c r="E13">
-        <v>1.325348115716708</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.90394577623963679</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14">
-        <v>232225.84310977679</v>
+        <v>113706.43058039621</v>
       </c>
       <c r="C14">
-        <v>138127.90909999999</v>
+        <v>124993.859</v>
       </c>
       <c r="D14">
-        <v>94097.9340097768</v>
+        <v>-11287.428419603761</v>
       </c>
       <c r="E14">
-        <v>1.6812376631405681</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.90969613619494893</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B15">
-        <v>113706.43058039621</v>
+        <v>6679.3387372576499</v>
       </c>
       <c r="C15">
-        <v>124993.859</v>
+        <v>7271</v>
       </c>
       <c r="D15">
-        <v>-11287.428419603761</v>
+        <v>-591.66126274235012</v>
       </c>
       <c r="E15">
-        <v>0.90969613619494893</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="3">
-        <v>7015.5469297352392</v>
-      </c>
-      <c r="C16" s="3">
-        <v>25315.878199999999</v>
-      </c>
-      <c r="D16" s="3">
-        <v>-18300.33127026476</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0.277120425146272</v>
+        <v>0.91862725034488379</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16">
+        <v>119997.1576154365</v>
+      </c>
+      <c r="C16">
+        <v>129512.8841</v>
+      </c>
+      <c r="D16">
+        <v>-9515.726484563449</v>
+      </c>
+      <c r="E16">
+        <v>0.92652679653696746</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B17">
-        <v>20238.81830973483</v>
+        <v>181786.2801864825</v>
       </c>
       <c r="C17">
-        <v>20107.965</v>
+        <v>195814.68040000001</v>
       </c>
       <c r="D17">
-        <v>130.8533097348263</v>
+        <v>-14028.400213517511</v>
       </c>
       <c r="E17">
-        <v>1.0065075361795599</v>
+        <v>0.92835879217604611</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B18">
-        <v>124842.74883</v>
+        <v>291924.3013799793</v>
       </c>
       <c r="C18">
-        <v>19248.270400000001</v>
+        <v>294608.3971</v>
       </c>
       <c r="D18">
-        <v>105594.47843</v>
+        <v>-2684.0957200207049</v>
       </c>
       <c r="E18">
-        <v>6.4859203572909072</v>
+        <v>0.99088927625131595</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B19">
-        <v>10558.860176517979</v>
+        <v>36931.116935558202</v>
       </c>
       <c r="C19">
-        <v>21634.757000000001</v>
+        <v>37245.561999999998</v>
       </c>
       <c r="D19">
-        <v>-11075.89682348202</v>
+        <v>-314.44506444180303</v>
       </c>
       <c r="E19">
-        <v>0.48805078682039171</v>
+        <v>0.99155751591446506</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B20">
-        <v>9108.190113087674</v>
+        <v>36676.523886086383</v>
       </c>
       <c r="C20">
-        <v>26796.345969999998</v>
+        <v>36874.774010000001</v>
       </c>
       <c r="D20">
-        <v>-17688.155856912319</v>
+        <v>-198.2501239136254</v>
       </c>
       <c r="E20">
-        <v>0.33990418407363449</v>
+        <v>0.99462369250426153</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>35578.001059861519</v>
+        <v>20238.81830973483</v>
       </c>
       <c r="C21">
-        <v>56107.381999999998</v>
+        <v>20107.965</v>
       </c>
       <c r="D21">
-        <v>-20529.380940138479</v>
+        <v>130.8533097348263</v>
       </c>
       <c r="E21">
-        <v>0.63410552750191629</v>
+        <v>1.0065075361795599</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B22">
-        <v>291924.3013799793</v>
+        <v>74891.213464487286</v>
       </c>
       <c r="C22">
-        <v>294608.3971</v>
+        <v>72492</v>
       </c>
       <c r="D22">
-        <v>-2684.0957200207049</v>
+        <v>2399.2134644872858</v>
       </c>
       <c r="E22">
-        <v>0.99088927625131595</v>
+        <v>1.0330962515103359</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="3">
-        <v>36251.555083860068</v>
-      </c>
-      <c r="C23" s="3">
-        <v>12403.638000000001</v>
-      </c>
-      <c r="D23" s="3">
-        <v>23847.917083860069</v>
-      </c>
-      <c r="E23" s="3">
-        <v>2.9226550374865878</v>
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23">
+        <v>102581.64419203129</v>
+      </c>
+      <c r="C23">
+        <v>95697.622499999998</v>
+      </c>
+      <c r="D23">
+        <v>6884.021692031296</v>
+      </c>
+      <c r="E23">
+        <v>1.0719351381172639</v>
+      </c>
+      <c r="F23" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B24">
-        <v>36676.523886086383</v>
+        <v>63357.174757889348</v>
       </c>
       <c r="C24">
-        <v>36874.774010000001</v>
+        <v>57797.154413883101</v>
       </c>
       <c r="D24">
-        <v>-198.2501239136254</v>
+        <v>5560.0203440062469</v>
       </c>
       <c r="E24">
-        <v>0.99462369250426153</v>
+        <v>1.096198859621897</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B25">
-        <v>14662.913501907869</v>
+        <v>30049.933466104401</v>
       </c>
       <c r="C25">
-        <v>16417.766</v>
+        <v>23332.800200000001</v>
       </c>
       <c r="D25">
-        <v>-1754.85249809213</v>
+        <v>6717.1332661043962</v>
       </c>
       <c r="E25">
-        <v>0.89311258924678727</v>
+        <v>1.2878837177075899</v>
+      </c>
+      <c r="F25" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B26">
-        <v>36931.116935558202</v>
+        <v>146455.53884009109</v>
       </c>
       <c r="C26">
-        <v>37245.561999999998</v>
+        <v>110503.4497</v>
       </c>
       <c r="D26">
-        <v>-314.44506444180303</v>
+        <v>35952.089140091062</v>
       </c>
       <c r="E26">
-        <v>0.99155751591446506</v>
+        <v>1.325348115716708</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="3">
-        <v>10809.1719204319</v>
-      </c>
-      <c r="C27" s="3">
-        <v>4109</v>
-      </c>
-      <c r="D27" s="3">
-        <v>6700.1719204319033</v>
-      </c>
-      <c r="E27" s="3">
-        <v>2.6306088879123641</v>
-      </c>
-      <c r="F27" t="s">
-        <v>40</v>
+      <c r="A27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>374101.62411073368</v>
+      </c>
+      <c r="C27">
+        <v>253807.72769999999</v>
+      </c>
+      <c r="D27">
+        <v>120293.8964107338</v>
+      </c>
+      <c r="E27">
+        <v>1.4739567920206149</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B28">
-        <v>30198.711343158309</v>
+        <v>23612.49945893959</v>
       </c>
       <c r="C28">
-        <v>33407.658000000003</v>
+        <v>15908.3</v>
       </c>
       <c r="D28">
-        <v>-3208.9466568416901</v>
+        <v>7704.1994589395936</v>
       </c>
       <c r="E28">
-        <v>0.90394577623963679</v>
+        <v>1.4842880420245781</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="B29">
-        <v>9150.1771490981282</v>
+        <v>40875.432077647783</v>
       </c>
       <c r="C29">
-        <v>14214.106</v>
+        <v>27335.623950000001</v>
       </c>
       <c r="D29">
-        <v>-5063.9288509018716</v>
+        <v>13539.808127647781</v>
       </c>
       <c r="E29">
-        <v>0.64373919464918361</v>
+        <v>1.495317324836398</v>
+      </c>
+      <c r="F29" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="B30">
-        <v>28000.734119851651</v>
+        <v>232225.84310977679</v>
       </c>
       <c r="C30">
-        <v>45467.192990000003</v>
+        <v>138127.90909999999</v>
       </c>
       <c r="D30">
-        <v>-17466.458870148352</v>
+        <v>94097.9340097768</v>
       </c>
       <c r="E30">
-        <v>0.61584479442155349</v>
+        <v>1.6812376631405681</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31">
-        <v>181786.2801864825</v>
-      </c>
-      <c r="C31">
-        <v>195814.68040000001</v>
-      </c>
-      <c r="D31">
-        <v>-14028.400213517511</v>
-      </c>
-      <c r="E31">
-        <v>0.92835879217604611</v>
+      <c r="A31" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3">
+        <v>10809.1719204319</v>
+      </c>
+      <c r="C31" s="3">
+        <v>4109</v>
+      </c>
+      <c r="D31" s="3">
+        <v>6700.1719204319033</v>
+      </c>
+      <c r="E31" s="3">
+        <v>2.6306088879123641</v>
+      </c>
+      <c r="F31" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32">
-        <v>13637.62339983279</v>
-      </c>
-      <c r="C32">
-        <v>18188</v>
-      </c>
-      <c r="D32">
-        <v>-4550.3766001672138</v>
-      </c>
-      <c r="E32">
-        <v>0.74981435011176523</v>
+      <c r="A32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="3">
+        <v>36251.555083860068</v>
+      </c>
+      <c r="C32" s="3">
+        <v>12403.638000000001</v>
+      </c>
+      <c r="D32" s="3">
+        <v>23847.917083860069</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2.9226550374865878</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B33">
-        <v>6679.3387372576499</v>
+        <v>124842.74883</v>
       </c>
       <c r="C33">
-        <v>7271</v>
+        <v>19248.270400000001</v>
       </c>
       <c r="D33">
-        <v>-591.66126274235012</v>
+        <v>105594.47843</v>
       </c>
       <c r="E33">
-        <v>0.91862725034488379</v>
+        <v>6.4859203572909072</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G33" xr:uid="{685CFB30-F35F-4405-9D5F-B0945D39203A}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G33">
+      <sortCondition ref="E1:E33"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/Quality control/ghg_comparison__.xlsx
+++ b/data/Quality control/ghg_comparison__.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="48" documentId="11_23F921ED55A38BD86D7F8C426FB6CD627552AE68" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9126330-2142-49DC-B226-3444CCC9D3B2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -578,17 +578,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -608,7 +608,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -628,7 +628,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -645,7 +645,7 @@
         <v>0.92652679653696746</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -662,7 +662,7 @@
         <v>1.495317324836398</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -679,7 +679,7 @@
         <v>1.0719351381172639</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -696,7 +696,7 @@
         <v>1.4842880420245781</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -713,7 +713,7 @@
         <v>1.0330962515103359</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -730,7 +730,7 @@
         <v>1.4739567920206149</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -747,7 +747,7 @@
         <v>1.096198859621897</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -773,7 +773,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
@@ -796,7 +796,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
@@ -816,7 +816,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -833,7 +833,7 @@
         <v>1.325348115716708</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -850,7 +850,7 @@
         <v>1.6812376631405681</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -867,7 +867,7 @@
         <v>0.90969613619494893</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -884,7 +884,7 @@
         <v>0.277120425146272</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -901,7 +901,7 @@
         <v>1.0065075361795599</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
@@ -918,7 +918,7 @@
         <v>6.4859203572909072</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -935,7 +935,7 @@
         <v>0.48805078682039171</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -952,7 +952,7 @@
         <v>0.33990418407363449</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -969,7 +969,7 @@
         <v>0.63410552750191629</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -986,7 +986,7 @@
         <v>0.99088927625131595</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>26</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>2.9226550374865878</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>0.99462369250426153</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>0.89311258924678727</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>0.99155751591446506</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>30</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>0.90394577623963679</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>0.64373919464918361</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>0.61584479442155349</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>0.92835879217604611</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>0.74981435011176523</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -1185,17 +1185,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{685CFB30-F35F-4405-9D5F-B0945D39203A}">
   <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>0.277120425146272</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>0.33990418407363449</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>0.48805078682039171</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>33</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>0.61584479442155349</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>0.63410552750191629</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>0.64373919464918361</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>0.74981435011176523</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>0.89311258924678727</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>0.90394577623963679</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>0.90969613619494893</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>36</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>0.91862725034488379</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>0.92652679653696746</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>0.92835879217604611</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>0.99088927625131595</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>0.99155751591446506</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>0.99462369250426153</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>1.0065075361795599</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>1.0330962515103359</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>12</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>1.096198859621897</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>15</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>16</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>1.325348115716708</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>11</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>1.4739567920206149</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>9</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>1.4842880420245781</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>17</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>1.6812376631405681</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>26</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>2.9226550374865878</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>21</v>
       </c>
